--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.3002145912865</v>
+        <v>3.786284871084057</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5604951616792</v>
+        <v>2.691080463772869</v>
       </c>
       <c r="E2" t="n">
-        <v>18.71560465956468</v>
+        <v>3.041285757179262</v>
       </c>
       <c r="F2" t="n">
-        <v>19.88429687806811</v>
+        <v>3.231198242686068</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.12160015916074</v>
+        <v>4.08226002586362</v>
       </c>
       <c r="D3" t="n">
-        <v>20.08015464703144</v>
+        <v>3.263025130142609</v>
       </c>
       <c r="E3" t="n">
-        <v>18.71560465956468</v>
+        <v>3.041285757179262</v>
       </c>
       <c r="F3" t="n">
-        <v>19.88429687806811</v>
+        <v>3.231198242686068</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.88135325044529</v>
+        <v>10.38071990319736</v>
       </c>
       <c r="D4" t="n">
-        <v>60.39101159162664</v>
+        <v>9.813539383639331</v>
       </c>
       <c r="E4" t="n">
-        <v>18.71560465956468</v>
+        <v>3.041285757179262</v>
       </c>
       <c r="F4" t="n">
-        <v>19.88429687806811</v>
+        <v>3.231198242686068</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
